--- a/public/modelo-departamentos-equipe.xlsx
+++ b/public/modelo-departamentos-equipe.xlsx
@@ -1,53 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Departamentos" sheetId="1" r:id="rId1"/>
-    <sheet name="Equipe" sheetId="2" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipe" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -65,14 +41,84 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -397,270 +443,147 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="26.83203125" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" customWidth="1"/>
-    <col min="3" max="3" width="95.83203125" customWidth="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>Departamento</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Cidades que atende</v>
-      </c>
-      <c r="C1" t="str">
-        <v>O que esse departamento trata</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Nome completo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>E-mail (será o login)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Papel (Administrador, Gerente ou Atendente)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Departamento(s)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Cidade/unidade</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>WhatsApp (com DDD)</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>Atendimento Geral / SAC</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Todas</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Dúvidas gerais, troca de titularidade, atualização de cadastro, reclamações</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ana Souza</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ana@provedor.com.br</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Financeiro, Cobrança</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Todas</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>(43) 99666-1541</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>Financeiro</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Todas (centralizado na matriz)</v>
-      </c>
-      <c r="C3" t="str">
-        <v>2ª via de boleto, desbloqueio em confiança, negociação de débitos, alteração de vencimento, estorno</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Bruno Lima</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>bruno@provedor.com.br</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Gerente</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Suporte Técnico</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Todas</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>(43) 99111-2233</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>Cobrança</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Todas</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Contato com inadimplentes, parcelamento, aviso de corte</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Suporte Técnico N1</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Londrina</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Diagnóstico de conexão, reset de ONU, troca de senha e nome do Wi-Fi</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Suporte Técnico N1</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Cambé</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Diagnóstico de conexão, reset de ONU, troca de senha e nome do Wi-Fi</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Suporte Técnico N2</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Todas (equipe em Londrina)</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Casos escalados do N1, configurações avançadas, agendamento de visita técnica</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Comercial / Vendas</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Londrina</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Apresentação de planos, upgrades, novas instalações</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Comercial / Vendas</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Cambé</v>
-      </c>
-      <c r="C9" t="str">
-        <v>Apresentação de planos, upgrades, novas instalações</v>
-      </c>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Carla Nunes</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>carla@provedor.com.br</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Atendente</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Suporte Técnico</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Londrina</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C9"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E8"/>
-  <cols>
-    <col min="1" max="1" width="24.83203125" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" customWidth="1"/>
-    <col min="3" max="3" width="26.83203125" customWidth="1"/>
-    <col min="4" max="4" width="18.83203125" customWidth="1"/>
-    <col min="5" max="5" width="28.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Nome completo</v>
-      </c>
-      <c r="B1" t="str">
-        <v>E-mail (será o login)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Departamento(s)</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Cidade/unidade</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Papel (Gestor ou Atendente)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Ana Souza</v>
-      </c>
-      <c r="B2" t="str">
-        <v>ana@provedor.com.br</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Financeiro, Cobrança</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Todas</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Gestor</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Bruno Lima</v>
-      </c>
-      <c r="B3" t="str">
-        <v>bruno@provedor.com.br</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Financeiro</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Todas</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Atendente</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Carla Nunes</v>
-      </c>
-      <c r="B4" t="str">
-        <v>carla@provedor.com.br</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Suporte Técnico N1</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Londrina</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Atendente</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Diego Ramos</v>
-      </c>
-      <c r="B5" t="str">
-        <v>diego@provedor.com.br</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Suporte Técnico N1</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Cambé</v>
-      </c>
-      <c r="E5" t="str">
-        <v>Atendente</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Eduardo Alves</v>
-      </c>
-      <c r="B6" t="str">
-        <v>eduardo@provedor.com.br</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Suporte Técnico N2</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Todas</v>
-      </c>
-      <c r="E6" t="str">
-        <v>Gestor</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Fernanda Costa</v>
-      </c>
-      <c r="B7" t="str">
-        <v>fernanda@provedor.com.br</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Comercial / Vendas</v>
-      </c>
-      <c r="D7" t="str">
-        <v>Londrina</v>
-      </c>
-      <c r="E7" t="str">
-        <v>Atendente</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>João Pereira (sócio)</v>
-      </c>
-      <c r="B8" t="str">
-        <v>joao@provedor.com.br</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Todos</v>
-      </c>
-      <c r="D8" t="str">
-        <v>Todas</v>
-      </c>
-      <c r="E8" t="str">
-        <v>Gestor</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E8"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>